--- a/outputs/Cell output 5.xlsx
+++ b/outputs/Cell output 5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos_Python\kpis_carteira\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4CA0C9-6A01-4CE7-A44E-13146DC16F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AB390F-2158-4E87-8ECE-ECEDE4834B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6F69F660-98EB-4076-96B2-E124712A5C7D}"/>
   </bookViews>
@@ -264,7 +264,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
   <si>
     <t>Portfolio</t>
   </si>
@@ -429,14 +429,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="[$-416]mmmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="0.0000000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="0.0000%"/>
-    <numFmt numFmtId="172" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -583,6 +584,12 @@
       <color indexed="81"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="37">
@@ -1337,7 +1344,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1501,7 +1508,13 @@
     <xf numFmtId="0" fontId="16" fillId="35" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1896,7 +1909,7 @@
     <col min="12" max="12" width="15" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" style="2"/>
+    <col min="16" max="16" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="11.140625" style="2" customWidth="1"/>
     <col min="19" max="19" width="11.7109375" style="2" customWidth="1"/>
@@ -2304,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="AI3" s="31">
-        <f t="shared" ref="AI3:AJ66" si="21">F3-$H3</f>
+        <f t="shared" ref="AI3:AI66" si="21">F3-$H3</f>
         <v>-3.2874707254742175E-2</v>
       </c>
       <c r="AJ3" s="13">
@@ -11328,7 +11341,7 @@
         <v>0</v>
       </c>
       <c r="AI67" s="31">
-        <f t="shared" ref="AI67:AJ130" si="110">F67-$H67</f>
+        <f t="shared" ref="AI67:AI130" si="110">F67-$H67</f>
         <v>0.10910929980850603</v>
       </c>
       <c r="AJ67" s="13">
@@ -20352,7 +20365,7 @@
         <v>4.5403497368865448E-3</v>
       </c>
       <c r="AI131" s="31">
-        <f t="shared" ref="AI131:AJ182" si="199">F131-$H131</f>
+        <f t="shared" ref="AI131:AI182" si="199">F131-$H131</f>
         <v>-4.7651175346667518E-2</v>
       </c>
       <c r="AJ131" s="13">
@@ -27570,6 +27583,21 @@
       <c r="E184" s="2">
         <f>PRODUCT(I2:I182)</f>
         <v>2.6168963278262809</v>
+      </c>
+      <c r="O184" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P184" s="57">
+        <f>AVERAGE(P2:P182)</f>
+        <v>2.5828767175292228E-2</v>
+      </c>
+      <c r="Q184" s="57">
+        <f>AVERAGE(Q2:Q182)</f>
+        <v>-1.838256568170114E-2</v>
+      </c>
+      <c r="R184" s="57">
+        <f>AVERAGE(R2:R182)</f>
+        <v>4.0220347729963787E-2</v>
       </c>
       <c r="S184" s="1" t="s">
         <v>42</v>
@@ -27751,7 +27779,7 @@
       <c r="A198" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B198" s="2">
+      <c r="B198" s="56">
         <f>(AVERAGE(T2:T182)/_xlfn.STDEV.S(T2:T182))*SQRT(12)</f>
         <v>0.11356880688332176</v>
       </c>
@@ -27914,7 +27942,7 @@
   <autoFilter ref="A1:O182" xr:uid="{695E2C63-CFAD-4735-B42D-9836B3BF66DE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="Y2:Y182 AA2:AA182 Q2:Q182 AC2:AC182 AD2:AD182 AE2:AE182 AG2:AG182" formula="1"/>
+    <ignoredError sqref="Y2:Y182 AA2:AA182 Q2:Q182 AC2:AC182 AD2:AD182 AE2:AE182 AG2:AG182 R2:R182" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
